--- a/output/graficos_dimensiones/comunal_d_env_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:14</t>
+    <t xml:space="preserve">2026-09-10 01:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:28</t>
+    <t xml:space="preserve">2026-09-12 22:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_valparaiso.xlsx
@@ -96,12 +96,12 @@
     <t xml:space="preserve">Puchuncaví</t>
   </si>
   <si>
+    <t xml:space="preserve">Los Andes</t>
+  </si>
+  <si>
     <t xml:space="preserve">Villa Alemana</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Andes</t>
-  </si>
-  <si>
     <t xml:space="preserve">Concón</t>
   </si>
   <si>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:39</t>
+    <t xml:space="preserve">2026-09-24 00:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -589,7 +589,7 @@
         <v>2018</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>151.07</v>
+        <v>160.71</v>
       </c>
     </row>
     <row r="3">
@@ -606,7 +606,7 @@
         <v>2018</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>140.96</v>
+        <v>150.93</v>
       </c>
     </row>
     <row r="4">
@@ -623,7 +623,7 @@
         <v>2018</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>138.24</v>
+        <v>147.41</v>
       </c>
     </row>
     <row r="5">
@@ -640,7 +640,7 @@
         <v>2018</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>116.43</v>
+        <v>125.33</v>
       </c>
     </row>
     <row r="6">
@@ -657,7 +657,7 @@
         <v>2018</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>116.01</v>
+        <v>124.87</v>
       </c>
     </row>
     <row r="7">
@@ -674,7 +674,7 @@
         <v>2018</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>114.42</v>
+        <v>122.53</v>
       </c>
     </row>
     <row r="8">
@@ -691,7 +691,7 @@
         <v>2018</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>111.85</v>
+        <v>120.12</v>
       </c>
     </row>
     <row r="9">
@@ -708,7 +708,7 @@
         <v>2018</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>108.8</v>
+        <v>116.83</v>
       </c>
     </row>
     <row r="10">
@@ -716,16 +716,16 @@
         <v>5</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>5101</v>
+        <v>5801</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>107.96</v>
+        <v>116.33</v>
       </c>
     </row>
     <row r="11">
@@ -733,16 +733,16 @@
         <v>5</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>5801</v>
+        <v>5101</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>107.73</v>
+        <v>116.25</v>
       </c>
     </row>
     <row r="12">
@@ -759,7 +759,7 @@
         <v>2018</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>105.21</v>
+        <v>112.94</v>
       </c>
     </row>
     <row r="13">
@@ -776,7 +776,7 @@
         <v>2018</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>103.72</v>
+        <v>111.24</v>
       </c>
     </row>
     <row r="14">
@@ -793,7 +793,7 @@
         <v>2018</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>103.1</v>
+        <v>110.28</v>
       </c>
     </row>
     <row r="15">
@@ -810,7 +810,7 @@
         <v>2018</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>100.35</v>
+        <v>106.69</v>
       </c>
     </row>
     <row r="16">
@@ -827,7 +827,7 @@
         <v>2018</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>97.52</v>
+        <v>104.4</v>
       </c>
     </row>
     <row r="17">
@@ -844,7 +844,7 @@
         <v>2018</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>97.41</v>
+        <v>104.24</v>
       </c>
     </row>
     <row r="18">
@@ -861,7 +861,7 @@
         <v>2018</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>96.32</v>
+        <v>103.32</v>
       </c>
     </row>
     <row r="19">
@@ -878,7 +878,7 @@
         <v>2018</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>93.72</v>
+        <v>101.05</v>
       </c>
     </row>
     <row r="20">
@@ -895,7 +895,7 @@
         <v>2018</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>93.37</v>
+        <v>100.52</v>
       </c>
     </row>
     <row r="21">
@@ -912,7 +912,7 @@
         <v>2018</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>93.3</v>
+        <v>99.97</v>
       </c>
     </row>
     <row r="22">
@@ -929,7 +929,7 @@
         <v>2018</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>92.05</v>
+        <v>98.53</v>
       </c>
     </row>
     <row r="23">
@@ -940,13 +940,13 @@
         <v>26</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>5804</v>
+        <v>5301</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>89.4</v>
+        <v>96.29</v>
       </c>
     </row>
     <row r="24">
@@ -957,13 +957,13 @@
         <v>27</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>5301</v>
+        <v>5804</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2018</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>89.38</v>
+        <v>96.28</v>
       </c>
     </row>
     <row r="25">
@@ -980,7 +980,7 @@
         <v>2018</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>88.28</v>
+        <v>94.58</v>
       </c>
     </row>
     <row r="26">
@@ -997,7 +997,7 @@
         <v>2018</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>87.78</v>
+        <v>93.79</v>
       </c>
     </row>
     <row r="27">
@@ -1014,7 +1014,7 @@
         <v>2018</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>87.62</v>
+        <v>93.06</v>
       </c>
     </row>
     <row r="28">
@@ -1031,7 +1031,7 @@
         <v>2018</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>86.85</v>
+        <v>92.91</v>
       </c>
     </row>
     <row r="29">
@@ -1048,7 +1048,7 @@
         <v>2018</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>86.13</v>
+        <v>92.14</v>
       </c>
     </row>
     <row r="30">
@@ -1065,7 +1065,7 @@
         <v>2018</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>85.81</v>
+        <v>92.09</v>
       </c>
     </row>
     <row r="31">
@@ -1082,7 +1082,7 @@
         <v>2018</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>84.15</v>
+        <v>89.68</v>
       </c>
     </row>
     <row r="32">
@@ -1099,7 +1099,7 @@
         <v>2018</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>82.57</v>
+        <v>87.88</v>
       </c>
     </row>
     <row r="33">
@@ -1116,7 +1116,7 @@
         <v>2018</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>80.3</v>
+        <v>85.77</v>
       </c>
     </row>
     <row r="34">
@@ -1133,7 +1133,7 @@
         <v>2018</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>78.78</v>
+        <v>84.75</v>
       </c>
     </row>
     <row r="35">
@@ -1150,7 +1150,7 @@
         <v>2018</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>77.77</v>
+        <v>83.28</v>
       </c>
     </row>
     <row r="36">
@@ -1167,7 +1167,7 @@
         <v>2018</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>77.11</v>
+        <v>80</v>
       </c>
     </row>
     <row r="37">
@@ -1184,7 +1184,7 @@
         <v>2018</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>73.87</v>
+        <v>78.71</v>
       </c>
     </row>
     <row r="38">
@@ -1201,7 +1201,7 @@
         <v>2018</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>68.5</v>
+        <v>72.49</v>
       </c>
     </row>
     <row r="39">
@@ -1218,7 +1218,7 @@
         <v>2018</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>41.16</v>
+        <v>43.55</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:08</t>
+    <t xml:space="preserve">2026-10-02 15:39</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:39</t>
+    <t xml:space="preserve">2026-10-04 10:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_valparaiso.xlsx
@@ -153,7 +153,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:38</t>
+    <t xml:space="preserve">2026-10-05 16:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
